--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379090C6-7BB2-4D78-B44C-0A43B686B981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D76E577-8E34-4B98-A185-8F1B63F4C8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="368" windowWidth="21600" windowHeight="11054" tabRatio="864" firstSheet="11" activeTab="15" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="28680" yWindow="-225" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="11" activeTab="17" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -723,9 +723,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -796,7 +796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.4">
+    <row r="2" spans="1:23" ht="15.75">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -867,7 +867,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.4">
+    <row r="3" spans="1:23" ht="15.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -938,7 +938,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.4">
+    <row r="4" spans="1:23" ht="15.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.4">
+    <row r="5" spans="1:23" ht="15.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.4">
+    <row r="6" spans="1:23" ht="15.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.4">
+    <row r="7" spans="1:23" ht="15.75">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.4">
+    <row r="8" spans="1:23" ht="15.75">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.4">
+    <row r="9" spans="1:23" ht="15.75">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.4">
+    <row r="10" spans="1:23" ht="15.75">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.4">
+    <row r="11" spans="1:23" ht="15.75">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1517,9 +1517,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1596,7 +1596,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1858,7 +1858,7 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2274,7 +2274,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.4">
+    <row r="12" spans="1:25" ht="15.75">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.4">
+    <row r="13" spans="1:25" ht="15.75">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.4">
+    <row r="14" spans="1:25" ht="15.75">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.4">
+    <row r="15" spans="1:25" ht="15.75">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.4">
+    <row r="16" spans="1:25" ht="15.75">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.4">
+    <row r="17" spans="1:25" ht="15.75">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.4">
+    <row r="18" spans="1:25" ht="15.75">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2713,7 +2713,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.4">
+    <row r="19" spans="1:25" ht="15.75">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.4">
+    <row r="20" spans="1:25" ht="15.75">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.4">
+    <row r="21" spans="1:25" ht="15.75">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.4">
+    <row r="22" spans="1:25" ht="15.75">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.4">
+    <row r="23" spans="1:25" ht="15.75">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.4">
+    <row r="24" spans="1:25" ht="15.75">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.4">
+    <row r="25" spans="1:25" ht="15.75">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="15.4">
+    <row r="26" spans="1:25" ht="15.75">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -3290,9 +3290,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -3369,7 +3369,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15.4">
+    <row r="12" spans="1:25" ht="15.75">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.4">
+    <row r="13" spans="1:25" ht="15.75">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.4">
+    <row r="14" spans="1:25" ht="15.75">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.4">
+    <row r="15" spans="1:25" ht="15.75">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.4">
+    <row r="16" spans="1:25" ht="15.75">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="15.4">
+    <row r="17" spans="1:25" ht="15.75">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.4">
+    <row r="18" spans="1:25" ht="15.75">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="15.4">
+    <row r="19" spans="1:25" ht="15.75">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -4719,7 +4719,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
     </row>
-    <row r="20" spans="1:25" ht="15.4">
+    <row r="20" spans="1:25" ht="15.75">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.4">
+    <row r="21" spans="1:25" ht="15.75">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.4">
+    <row r="22" spans="1:25" ht="15.75">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -4949,9 +4949,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -6607,13 +6607,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="B1">
         <v>1</v>
       </c>
@@ -6653,8 +6653,11 @@
       <c r="N1">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6697,8 +6700,11 @@
       <c r="N2">
         <v>128</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -6741,8 +6747,11 @@
       <c r="N3">
         <v>77</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -6785,8 +6794,11 @@
       <c r="N4">
         <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6829,8 +6841,11 @@
       <c r="N5">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6873,8 +6888,11 @@
       <c r="N6">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -6917,8 +6935,11 @@
       <c r="N7">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -6961,8 +6982,11 @@
       <c r="N8">
         <v>-21</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -7005,8 +7029,11 @@
       <c r="N9">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7049,8 +7076,11 @@
       <c r="N10">
         <v>41</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7093,8 +7123,11 @@
       <c r="N11">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7136,6 +7169,9 @@
       </c>
       <c r="N12">
         <v>16</v>
+      </c>
+      <c r="O12">
+        <v>-16</v>
       </c>
     </row>
   </sheetData>
@@ -7148,13 +7184,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.86328125" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7197,8 +7233,11 @@
       <c r="O1">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -7244,8 +7283,11 @@
       <c r="O2">
         <v>33.200000000000003</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -7291,8 +7333,11 @@
       <c r="O3">
         <v>31.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -7338,8 +7383,11 @@
       <c r="O4">
         <v>31.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="P4">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -7385,8 +7433,11 @@
       <c r="O5">
         <v>27.2</v>
       </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="P5">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7432,8 +7483,11 @@
       <c r="O6">
         <v>19.2</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -7479,8 +7533,11 @@
       <c r="O7">
         <v>13.8</v>
       </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="P7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -7526,8 +7583,11 @@
       <c r="O8">
         <v>6.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -7573,8 +7633,11 @@
       <c r="O9">
         <v>10.8</v>
       </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7620,8 +7683,11 @@
       <c r="O10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="P10">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7667,8 +7733,11 @@
       <c r="O11">
         <v>14.1</v>
       </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="P11">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7712,6 +7781,9 @@
         <v>3</v>
       </c>
       <c r="O12">
+        <v>3</v>
+      </c>
+      <c r="P12">
         <v>3</v>
       </c>
     </row>
@@ -7725,13 +7797,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7771,8 +7843,11 @@
       <c r="N1">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7815,8 +7890,11 @@
       <c r="N2">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7859,8 +7937,11 @@
       <c r="N3">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7903,8 +7984,11 @@
       <c r="N4">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -7947,8 +8031,11 @@
       <c r="N5">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -7991,8 +8078,11 @@
       <c r="N6">
         <v>93</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -8035,8 +8125,11 @@
       <c r="N7">
         <v>-12</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -8079,8 +8172,11 @@
       <c r="N8">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -8118,7 +8214,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -8161,8 +8257,11 @@
       <c r="N10">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -8205,8 +8304,11 @@
       <c r="N11">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -8249,8 +8351,11 @@
       <c r="N12">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -8293,8 +8398,11 @@
       <c r="N13">
         <v>-10</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -8337,8 +8445,11 @@
       <c r="N14">
         <v>-10</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -8381,8 +8492,11 @@
       <c r="N15">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -8425,8 +8539,11 @@
       <c r="N16">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -8469,8 +8586,11 @@
       <c r="N17">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -8513,8 +8633,11 @@
       <c r="N18">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -8557,8 +8680,11 @@
       <c r="N19">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -8601,8 +8727,11 @@
       <c r="N20">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -8645,8 +8774,11 @@
       <c r="N21">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -8689,8 +8821,11 @@
       <c r="N22">
         <v>13</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -8733,8 +8868,11 @@
       <c r="N23">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -8743,6 +8881,9 @@
       </c>
       <c r="N24">
         <v>17</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8755,13 +8896,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:P24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="B1">
         <v>1</v>
       </c>
@@ -8804,8 +8945,11 @@
       <c r="O1">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8851,8 +8995,11 @@
       <c r="O2">
         <v>27.4</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -8898,8 +9045,11 @@
       <c r="O3">
         <v>27.7</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -8945,8 +9095,11 @@
       <c r="O4">
         <v>26.7</v>
       </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="P4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -8992,8 +9145,11 @@
       <c r="O5">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="P5">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -9039,8 +9195,11 @@
       <c r="O6">
         <v>26.3</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -9086,8 +9245,11 @@
       <c r="O7">
         <v>24.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="P7">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -9133,8 +9295,11 @@
       <c r="O8">
         <v>25.2</v>
       </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -9172,7 +9337,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -9218,8 +9383,11 @@
       <c r="O10">
         <v>12.2</v>
       </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="P10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -9265,8 +9433,11 @@
       <c r="O11">
         <v>9.6</v>
       </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="P11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -9312,8 +9483,11 @@
       <c r="O12">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="P12">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -9359,8 +9533,11 @@
       <c r="O13">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="P13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -9406,8 +9583,11 @@
       <c r="O14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="P14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -9453,8 +9633,11 @@
       <c r="O15">
         <v>6.4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="P15">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -9500,8 +9683,11 @@
       <c r="O16">
         <v>9.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="P16">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -9547,8 +9733,11 @@
       <c r="O17">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="P17">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -9594,8 +9783,11 @@
       <c r="O18">
         <v>14.9</v>
       </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="P18">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -9641,8 +9833,11 @@
       <c r="O19">
         <v>8.6</v>
       </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="P19">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -9688,8 +9883,11 @@
       <c r="O20">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="P20">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -9735,8 +9933,11 @@
       <c r="O21">
         <v>10.4</v>
       </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="P21">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -9782,8 +9983,11 @@
       <c r="O22">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="P22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -9829,8 +10033,11 @@
       <c r="O23">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="P23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -9842,6 +10049,9 @@
       </c>
       <c r="O24">
         <v>9.9</v>
+      </c>
+      <c r="P24">
+        <v>9.6999999999999993</v>
       </c>
     </row>
   </sheetData>
@@ -9855,9 +10065,9 @@
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="12" max="12" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -10403,8 +10613,8 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -10614,6 +10824,20 @@
       </c>
       <c r="D15">
         <v>118.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>87</v>
+      </c>
+      <c r="B16">
+        <v>2026</v>
+      </c>
+      <c r="C16">
+        <v>17</v>
+      </c>
+      <c r="D16">
+        <v>120.9</v>
       </c>
     </row>
   </sheetData>
@@ -10627,9 +10851,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -10706,7 +10930,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -10783,7 +11007,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -10860,7 +11084,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -10937,7 +11161,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -11014,7 +11238,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -11091,7 +11315,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -11168,7 +11392,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -11245,7 +11469,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -11322,7 +11546,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -11399,7 +11623,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -11487,7 +11711,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -11563,7 +11787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -11640,7 +11864,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -11717,7 +11941,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -11794,7 +12018,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -11871,7 +12095,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -11948,7 +12172,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -12025,7 +12249,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -12102,7 +12326,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -12179,7 +12403,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -12256,7 +12480,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -12344,7 +12568,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
       <c r="B1">
@@ -12414,7 +12638,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.4">
+    <row r="2" spans="1:23" ht="15.75">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -12485,7 +12709,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.4">
+    <row r="3" spans="1:23" ht="15.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12556,7 +12780,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.4">
+    <row r="4" spans="1:23" ht="15.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12627,7 +12851,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.4">
+    <row r="5" spans="1:23" ht="15.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12698,7 +12922,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.4">
+    <row r="6" spans="1:23" ht="15.75">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -12769,7 +12993,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.4">
+    <row r="7" spans="1:23" ht="15.75">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -12840,7 +13064,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.4">
+    <row r="8" spans="1:23" ht="15.75">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -12911,7 +13135,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.4">
+    <row r="9" spans="1:23" ht="15.75">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -12982,7 +13206,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.4">
+    <row r="10" spans="1:23" ht="15.75">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -13053,7 +13277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.4">
+    <row r="11" spans="1:23" ht="15.75">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -13135,7 +13359,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -13211,7 +13435,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -13288,7 +13512,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -13365,7 +13589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13442,7 +13666,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -13519,7 +13743,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -13596,7 +13820,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -13673,7 +13897,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -13750,7 +13974,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -13827,7 +14051,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -13904,7 +14128,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -13992,7 +14216,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -14849,9 +15073,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" customHeight="1">
@@ -14922,7 +15146,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.4">
+    <row r="2" spans="1:23" ht="15.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -14993,7 +15217,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.4">
+    <row r="3" spans="1:23" ht="15.75">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -15064,7 +15288,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.4">
+    <row r="4" spans="1:23" ht="15.75">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -15135,7 +15359,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.4">
+    <row r="5" spans="1:23" ht="15.75">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -15206,7 +15430,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.4">
+    <row r="6" spans="1:23" ht="15.75">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -15277,7 +15501,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.4">
+    <row r="7" spans="1:23" ht="15.75">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -15348,7 +15572,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.4">
+    <row r="8" spans="1:23" ht="15.75">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -15419,7 +15643,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.4">
+    <row r="9" spans="1:23" ht="15.75">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -15490,7 +15714,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.4">
+    <row r="10" spans="1:23" ht="15.75">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -15561,7 +15785,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.4">
+    <row r="11" spans="1:23" ht="15.75">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -15632,7 +15856,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.4">
+    <row r="12" spans="1:23" ht="15.75">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -15703,7 +15927,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.4">
+    <row r="13" spans="1:23" ht="15.75">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -15774,7 +15998,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.4">
+    <row r="14" spans="1:23" ht="15.75">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -15845,7 +16069,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.4">
+    <row r="15" spans="1:23" ht="15.75">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -15916,7 +16140,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.4">
+    <row r="16" spans="1:23" ht="15.75">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -15987,7 +16211,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.4">
+    <row r="17" spans="1:23" ht="15.75">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -16058,7 +16282,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.4">
+    <row r="18" spans="1:23" ht="15.75">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -16129,7 +16353,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="15.4">
+    <row r="19" spans="1:23" ht="15.75">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -16166,7 +16390,7 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="1:23" ht="15.4">
+    <row r="20" spans="1:23" ht="15.75">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -16207,7 +16431,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.4">
+    <row r="21" spans="1:23" ht="15.75">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -16254,7 +16478,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.4">
+    <row r="22" spans="1:23" ht="15.75">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -16325,7 +16549,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.4">
+    <row r="23" spans="1:23" ht="15.75">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -16407,9 +16631,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -16480,7 +16704,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.4">
+    <row r="2" spans="1:23" ht="15.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -16551,7 +16775,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.4">
+    <row r="3" spans="1:23" ht="15.75">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -16622,7 +16846,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.4">
+    <row r="4" spans="1:23" ht="15.75">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -16693,7 +16917,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.4">
+    <row r="5" spans="1:23" ht="15.75">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -16764,7 +16988,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.4">
+    <row r="6" spans="1:23" ht="15.75">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -16835,7 +17059,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.4">
+    <row r="7" spans="1:23" ht="15.75">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -16906,7 +17130,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.4">
+    <row r="8" spans="1:23" ht="15.75">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -16977,7 +17201,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.4">
+    <row r="9" spans="1:23" ht="15.75">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -17048,7 +17272,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.4">
+    <row r="10" spans="1:23" ht="15.75">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -17119,7 +17343,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.4">
+    <row r="11" spans="1:23" ht="15.75">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -17190,7 +17414,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.4">
+    <row r="12" spans="1:23" ht="15.75">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -17261,7 +17485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.4">
+    <row r="13" spans="1:23" ht="15.75">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -17332,7 +17556,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.4">
+    <row r="14" spans="1:23" ht="15.75">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -17373,7 +17597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.4">
+    <row r="15" spans="1:23" ht="15.75">
       <c r="A15" t="s">
         <v>79</v>
       </c>
@@ -17444,7 +17668,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.4">
+    <row r="16" spans="1:23" ht="15.75">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -17515,7 +17739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.4">
+    <row r="17" spans="1:23" ht="15.75">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -17586,7 +17810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.4">
+    <row r="18" spans="1:23" ht="15.75">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -17623,7 +17847,7 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="1:23" ht="15.4">
+    <row r="19" spans="1:23" ht="15.75">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -17694,7 +17918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="15.4">
+    <row r="20" spans="1:23" ht="15.75">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -17765,7 +17989,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.4">
+    <row r="21" spans="1:23" ht="15.75">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -17812,7 +18036,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.4">
+    <row r="22" spans="1:23" ht="15.75">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -17883,7 +18107,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.4">
+    <row r="23" spans="1:23" ht="15.75">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -17965,9 +18189,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -18044,7 +18268,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -18121,7 +18345,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -18198,7 +18422,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -18275,7 +18499,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -18352,7 +18576,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -18429,7 +18653,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -18506,7 +18730,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -18581,7 +18805,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -18658,7 +18882,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -18735,7 +18959,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -18768,7 +18992,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.4">
+    <row r="12" spans="1:25" ht="15.75">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -18799,7 +19023,7 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" spans="1:25" ht="15.4">
+    <row r="13" spans="1:25" ht="15.75">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -18876,7 +19100,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.4">
+    <row r="14" spans="1:25" ht="15.75">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -18907,7 +19131,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.4">
+    <row r="15" spans="1:25" ht="15.75">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -18948,7 +19172,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.4">
+    <row r="16" spans="1:25" ht="15.75">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -19023,7 +19247,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.4">
+    <row r="17" spans="1:25" ht="15.75">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -19096,7 +19320,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.4">
+    <row r="18" spans="1:25" ht="15.75">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -19161,7 +19385,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.4">
+    <row r="19" spans="1:25" ht="15.75">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -19238,7 +19462,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.4">
+    <row r="20" spans="1:25" ht="15.75">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -19315,7 +19539,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.4">
+    <row r="21" spans="1:25" ht="15.75">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -19392,7 +19616,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.4">
+    <row r="22" spans="1:25" ht="15.75">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -19469,7 +19693,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.4">
+    <row r="23" spans="1:25" ht="15.75">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -19546,7 +19770,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.4">
+    <row r="24" spans="1:25" ht="15.75">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -19623,7 +19847,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.4">
+    <row r="25" spans="1:25" ht="15.75">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -19670,7 +19894,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15.4">
+    <row r="26" spans="1:25" ht="15.75">
       <c r="A26" t="s">
         <v>41</v>
       </c>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D76E577-8E34-4B98-A185-8F1B63F4C8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9810568D-0CB1-494E-BD75-099550687546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-225" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="11" activeTab="17" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="864" firstSheet="11" activeTab="17" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -376,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -384,6 +384,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -723,9 +729,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -796,7 +802,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -867,7 +873,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -938,7 +944,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1009,7 +1015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1080,7 +1086,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1151,7 +1157,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1222,7 +1228,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1293,7 +1299,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1364,7 +1370,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1435,7 +1441,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1517,9 +1523,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1596,7 +1602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1673,7 +1679,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1750,7 +1756,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1827,7 +1833,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1858,7 +1864,7 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1935,7 +1941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2010,7 +2016,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2087,7 +2093,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2164,7 +2170,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -2241,7 +2247,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2274,7 +2280,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75">
+    <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -2305,7 +2311,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.75">
+    <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -2378,7 +2384,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.75">
+    <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -2455,7 +2461,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75">
+    <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -2496,7 +2502,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75">
+    <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -2571,7 +2577,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.75">
+    <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -2648,7 +2654,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.75">
+    <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2713,7 +2719,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.75">
+    <row r="19" spans="1:25" ht="15.4">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2790,7 +2796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.75">
+    <row r="20" spans="1:25" ht="15.4">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -2867,7 +2873,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75">
+    <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -2944,7 +2950,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75">
+    <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -3021,7 +3027,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.75">
+    <row r="23" spans="1:25" ht="15.4">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3098,7 +3104,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.75">
+    <row r="24" spans="1:25" ht="15.4">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -3145,7 +3151,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.75">
+    <row r="25" spans="1:25" ht="15.4">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -3202,7 +3208,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="15.75">
+    <row r="26" spans="1:25" ht="15.4">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -3290,9 +3296,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -3369,7 +3375,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3446,7 +3452,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3523,7 +3529,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3600,7 +3606,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -3677,7 +3683,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3754,7 +3760,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -3831,7 +3837,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -3908,7 +3914,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -3985,7 +3991,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -4062,7 +4068,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -4139,7 +4145,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15.75">
+    <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -4216,7 +4222,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.75">
+    <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -4293,7 +4299,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.75">
+    <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -4370,7 +4376,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75">
+    <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -4447,7 +4453,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75">
+    <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -4524,7 +4530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="15.75">
+    <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -4601,7 +4607,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.75">
+    <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -4678,7 +4684,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="15.75">
+    <row r="19" spans="1:25" ht="15.4">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -4719,7 +4725,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
     </row>
-    <row r="20" spans="1:25" ht="15.75">
+    <row r="20" spans="1:25" ht="15.4">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -4796,7 +4802,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75">
+    <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -4873,7 +4879,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75">
+    <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -4949,9 +4955,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -6607,13 +6613,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:Q12"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="B1">
         <v>1</v>
       </c>
@@ -6624,40 +6630,46 @@
         <v>3</v>
       </c>
       <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
         <v>6</v>
       </c>
-      <c r="F1">
+      <c r="H1">
         <v>7</v>
       </c>
-      <c r="G1">
+      <c r="I1">
         <v>8</v>
       </c>
-      <c r="H1">
+      <c r="J1">
         <v>9</v>
       </c>
-      <c r="I1">
+      <c r="K1">
         <v>10</v>
       </c>
-      <c r="J1">
+      <c r="L1">
         <v>11</v>
       </c>
-      <c r="K1">
+      <c r="M1">
         <v>12</v>
       </c>
-      <c r="L1">
+      <c r="N1">
         <v>13</v>
       </c>
-      <c r="M1">
+      <c r="O1">
         <v>14</v>
       </c>
-      <c r="N1">
+      <c r="P1">
         <v>15</v>
       </c>
-      <c r="O1">
+      <c r="Q1">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6703,8 +6715,14 @@
       <c r="O2">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2">
+        <v>88</v>
+      </c>
+      <c r="Q2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -6750,8 +6768,14 @@
       <c r="O3">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -6797,8 +6821,14 @@
       <c r="O4">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="P4">
+        <v>71</v>
+      </c>
+      <c r="Q4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6844,8 +6874,14 @@
       <c r="O5">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="P5">
+        <v>45</v>
+      </c>
+      <c r="Q5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6891,8 +6927,14 @@
       <c r="O6">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6">
+        <v>-18</v>
+      </c>
+      <c r="Q6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -6938,8 +6980,14 @@
       <c r="O7">
         <v>-11</v>
       </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="P7">
+        <v>6</v>
+      </c>
+      <c r="Q7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -6985,8 +7033,14 @@
       <c r="O8">
         <v>-17</v>
       </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8">
+        <v>-35</v>
+      </c>
+      <c r="Q8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -7032,8 +7086,14 @@
       <c r="O9">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9">
+        <v>21</v>
+      </c>
+      <c r="Q9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7079,8 +7139,14 @@
       <c r="O10">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="P10">
+        <v>27</v>
+      </c>
+      <c r="Q10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7126,8 +7192,14 @@
       <c r="O11">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="P11">
+        <v>23</v>
+      </c>
+      <c r="Q11">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7172,6 +7244,12 @@
       </c>
       <c r="O12">
         <v>-16</v>
+      </c>
+      <c r="P12">
+        <v>16</v>
+      </c>
+      <c r="Q12">
+        <v>-12</v>
       </c>
     </row>
   </sheetData>
@@ -7184,13 +7262,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:R12"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7201,43 +7279,49 @@
         <v>3</v>
       </c>
       <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
         <v>6</v>
       </c>
-      <c r="F1">
+      <c r="H1">
         <v>7</v>
       </c>
-      <c r="G1">
+      <c r="I1">
         <v>8</v>
       </c>
-      <c r="H1">
+      <c r="J1">
         <v>9</v>
       </c>
-      <c r="I1">
+      <c r="K1">
         <v>10</v>
       </c>
-      <c r="J1">
+      <c r="L1">
         <v>11</v>
       </c>
-      <c r="K1">
+      <c r="M1">
         <v>12</v>
       </c>
-      <c r="L1">
+      <c r="N1">
         <v>13</v>
       </c>
-      <c r="M1">
+      <c r="O1">
         <v>14</v>
       </c>
-      <c r="N1">
+      <c r="P1">
         <v>15</v>
       </c>
-      <c r="O1">
+      <c r="Q1">
         <v>16</v>
       </c>
-      <c r="P1">
+      <c r="R1">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -7286,8 +7370,14 @@
       <c r="P2">
         <v>33.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="R2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -7336,8 +7426,14 @@
       <c r="P3">
         <v>31.9</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="R3">
+        <v>32.299999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -7386,8 +7482,14 @@
       <c r="P4">
         <v>31.8</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4">
+        <v>32.1</v>
+      </c>
+      <c r="R4">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -7436,8 +7538,14 @@
       <c r="P5">
         <v>27.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5">
+        <v>27.6</v>
+      </c>
+      <c r="R5">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7486,8 +7594,14 @@
       <c r="P6">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="R6">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -7536,8 +7650,14 @@
       <c r="P7">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7">
+        <v>13.8</v>
+      </c>
+      <c r="R7">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -7586,8 +7706,14 @@
       <c r="P8">
         <v>6.3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8">
+        <v>5.7</v>
+      </c>
+      <c r="R8">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -7636,8 +7762,14 @@
       <c r="P9">
         <v>10.199999999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9">
+        <v>10.8</v>
+      </c>
+      <c r="R9">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7686,8 +7818,14 @@
       <c r="P10">
         <v>8.6</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="R10">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7736,8 +7874,14 @@
       <c r="P11">
         <v>14.7</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11">
+        <v>15.3</v>
+      </c>
+      <c r="R11">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7784,6 +7928,12 @@
         <v>3</v>
       </c>
       <c r="P12">
+        <v>3</v>
+      </c>
+      <c r="Q12">
+        <v>3.6</v>
+      </c>
+      <c r="R12">
         <v>3</v>
       </c>
     </row>
@@ -7797,13 +7947,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:Q24"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7814,40 +7964,46 @@
         <v>3</v>
       </c>
       <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
         <v>6</v>
       </c>
-      <c r="F1">
+      <c r="H1">
         <v>7</v>
       </c>
-      <c r="G1">
+      <c r="I1">
         <v>8</v>
       </c>
-      <c r="H1">
+      <c r="J1">
         <v>9</v>
       </c>
-      <c r="I1">
+      <c r="K1">
         <v>10</v>
       </c>
-      <c r="J1">
+      <c r="L1">
         <v>11</v>
       </c>
-      <c r="K1">
+      <c r="M1">
         <v>12</v>
       </c>
-      <c r="L1">
+      <c r="N1">
         <v>13</v>
       </c>
-      <c r="M1">
+      <c r="O1">
         <v>14</v>
       </c>
-      <c r="N1">
+      <c r="P1">
         <v>15</v>
       </c>
-      <c r="O1">
+      <c r="Q1">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7893,8 +8049,14 @@
       <c r="O2">
         <v>38</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2">
+        <v>43</v>
+      </c>
+      <c r="Q2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7940,8 +8102,14 @@
       <c r="O3">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3">
+        <v>45</v>
+      </c>
+      <c r="Q3">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7987,8 +8155,14 @@
       <c r="O4">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="P4">
+        <v>-11</v>
+      </c>
+      <c r="Q4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -8034,8 +8208,14 @@
       <c r="O5">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -8081,8 +8261,14 @@
       <c r="O6">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6">
+        <v>28</v>
+      </c>
+      <c r="Q6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -8128,8 +8314,14 @@
       <c r="O7">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="P7">
+        <v>20</v>
+      </c>
+      <c r="Q7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -8175,8 +8367,14 @@
       <c r="O8">
         <v>-13</v>
       </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8">
+        <v>15</v>
+      </c>
+      <c r="Q8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -8213,8 +8411,14 @@
       <c r="L9">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9">
+        <v>26</v>
+      </c>
+      <c r="Q9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -8260,8 +8464,14 @@
       <c r="O10">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="P10">
+        <v>-15</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -8307,8 +8517,14 @@
       <c r="O11">
         <v>-18</v>
       </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="P11">
+        <v>15</v>
+      </c>
+      <c r="Q11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -8354,8 +8570,14 @@
       <c r="O12">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="P12">
+        <v>-16</v>
+      </c>
+      <c r="Q12">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -8401,8 +8623,14 @@
       <c r="O13">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="P13">
+        <v>-14</v>
+      </c>
+      <c r="Q13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -8448,8 +8676,14 @@
       <c r="O14">
         <v>-22</v>
       </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="P14">
+        <v>-20</v>
+      </c>
+      <c r="Q14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -8495,8 +8729,14 @@
       <c r="O15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="P15">
+        <v>6</v>
+      </c>
+      <c r="Q15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -8542,8 +8782,14 @@
       <c r="O16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="P16">
+        <v>12</v>
+      </c>
+      <c r="Q16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -8589,8 +8835,14 @@
       <c r="O17">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="P17">
+        <v>15</v>
+      </c>
+      <c r="Q17">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -8636,8 +8888,14 @@
       <c r="O18">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="P18">
+        <v>3</v>
+      </c>
+      <c r="Q18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -8683,8 +8941,14 @@
       <c r="O19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="P19">
+        <v>8</v>
+      </c>
+      <c r="Q19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -8730,8 +8994,14 @@
       <c r="O20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="P20">
+        <v>17</v>
+      </c>
+      <c r="Q20">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -8777,8 +9047,14 @@
       <c r="O21">
         <v>13</v>
       </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="P21">
+        <v>-18</v>
+      </c>
+      <c r="Q21">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -8824,8 +9100,14 @@
       <c r="O22">
         <v>-18</v>
       </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="P22">
+        <v>11</v>
+      </c>
+      <c r="Q22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -8871,8 +9153,14 @@
       <c r="O23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="P23">
+        <v>6</v>
+      </c>
+      <c r="Q23">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -8896,13 +9184,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="B1">
         <v>1</v>
       </c>
@@ -8913,43 +9201,49 @@
         <v>3</v>
       </c>
       <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
         <v>6</v>
       </c>
-      <c r="F1">
+      <c r="H1">
         <v>7</v>
       </c>
-      <c r="G1">
+      <c r="I1">
         <v>8</v>
       </c>
-      <c r="H1">
+      <c r="J1">
         <v>9</v>
       </c>
-      <c r="I1">
+      <c r="K1">
         <v>10</v>
       </c>
-      <c r="J1">
+      <c r="L1">
         <v>11</v>
       </c>
-      <c r="K1">
+      <c r="M1">
         <v>12</v>
       </c>
-      <c r="L1">
+      <c r="N1">
         <v>13</v>
       </c>
-      <c r="M1">
+      <c r="O1">
         <v>14</v>
       </c>
-      <c r="N1">
+      <c r="P1">
         <v>15</v>
       </c>
-      <c r="O1">
+      <c r="Q1">
         <v>16</v>
       </c>
-      <c r="P1">
+      <c r="R1">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8998,8 +9292,14 @@
       <c r="P2">
         <v>27.3</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2">
+        <v>27.6</v>
+      </c>
+      <c r="R2">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9048,8 +9348,14 @@
       <c r="P3">
         <v>27.8</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3">
+        <v>28.1</v>
+      </c>
+      <c r="R3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -9098,8 +9404,14 @@
       <c r="P4">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4">
+        <v>26.7</v>
+      </c>
+      <c r="R4">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -9148,8 +9460,14 @@
       <c r="P5">
         <v>24.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5">
+        <v>24</v>
+      </c>
+      <c r="R5">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -9198,8 +9516,14 @@
       <c r="P6">
         <v>26.6</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6">
+        <v>26.9</v>
+      </c>
+      <c r="R6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -9248,8 +9572,14 @@
       <c r="P7">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7">
+        <v>23.7</v>
+      </c>
+      <c r="R7">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -9298,8 +9628,14 @@
       <c r="P8">
         <v>24.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8">
+        <v>24.6</v>
+      </c>
+      <c r="R8">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -9336,8 +9672,14 @@
       <c r="L9">
         <v>13.9</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9">
+        <v>15.1</v>
+      </c>
+      <c r="R9">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -9386,8 +9728,14 @@
       <c r="P10">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10">
+        <v>11.4</v>
+      </c>
+      <c r="R10">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -9436,8 +9784,14 @@
       <c r="P11">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11">
+        <v>8.4</v>
+      </c>
+      <c r="R11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -9486,8 +9840,14 @@
       <c r="P12">
         <v>6.4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12">
+        <v>5.8</v>
+      </c>
+      <c r="R12">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -9536,8 +9896,14 @@
       <c r="P13">
         <v>6.8</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13">
+        <v>6.2</v>
+      </c>
+      <c r="R13">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -9586,8 +9952,14 @@
       <c r="P14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14">
+        <v>3</v>
+      </c>
+      <c r="R14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -9636,8 +10008,14 @@
       <c r="P15">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15">
+        <v>5.6</v>
+      </c>
+      <c r="R15">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -9686,8 +10064,14 @@
       <c r="P16">
         <v>8.9</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16">
+        <v>9.1</v>
+      </c>
+      <c r="R16">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -9736,8 +10120,14 @@
       <c r="P17">
         <v>4.8</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17">
+        <v>5.4</v>
+      </c>
+      <c r="R17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -9786,8 +10176,14 @@
       <c r="P18">
         <v>15.1</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18">
+        <v>9.1</v>
+      </c>
+      <c r="R18">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -9836,8 +10232,14 @@
       <c r="P19">
         <v>8.4</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="R19">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -9886,8 +10288,14 @@
       <c r="P20">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="R20">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -9936,8 +10344,14 @@
       <c r="P21">
         <v>10.6</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21">
+        <v>10</v>
+      </c>
+      <c r="R21">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -9986,8 +10400,14 @@
       <c r="P22">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22">
+        <v>3</v>
+      </c>
+      <c r="R22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -10036,8 +10456,14 @@
       <c r="P23">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="Q23">
+        <v>3.6</v>
+      </c>
+      <c r="R23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -10056,6 +10482,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10065,9 +10492,9 @@
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -10613,231 +11040,259 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" t="s">
+      <c r="A1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2">
+      <c r="A2" s="4">
+        <v>71</v>
+      </c>
+      <c r="B2" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="4">
+        <v>72</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4">
+        <v>100.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="4">
         <v>73</v>
       </c>
-      <c r="B2">
+      <c r="B4" s="4">
         <v>2026</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
+      <c r="C4" s="4">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4">
+        <v>103.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="4">
+        <v>76</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C5" s="4">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4">
+        <v>104.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="4">
+        <v>77</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="4">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4">
+        <v>105.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="4">
+        <v>78</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C7" s="4">
+        <v>6</v>
+      </c>
+      <c r="D7" s="4">
+        <v>105.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="4">
+        <v>79</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C8" s="4">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4">
+        <v>104.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="4">
+        <v>80</v>
+      </c>
+      <c r="B9" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C9" s="4">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4">
+        <v>106.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="4">
+        <v>81</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C10" s="4">
+        <v>9</v>
+      </c>
+      <c r="D10" s="4">
+        <v>108.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="4">
+        <v>82</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C11" s="4">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4">
+        <v>110.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="4">
+        <v>83</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C12" s="4">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4">
+        <v>113.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="4">
+        <v>84</v>
+      </c>
+      <c r="B13" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C13" s="4">
+        <v>12</v>
+      </c>
+      <c r="D13" s="4">
+        <v>115.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="4">
+        <v>85</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C14" s="4">
+        <v>13</v>
+      </c>
+      <c r="D14" s="4">
+        <v>116.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="4">
+        <v>86</v>
+      </c>
+      <c r="B15" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C15" s="4">
+        <v>14</v>
+      </c>
+      <c r="D15" s="4">
+        <v>118.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="4">
+        <v>87</v>
+      </c>
+      <c r="B16" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C16" s="4">
+        <v>15</v>
+      </c>
+      <c r="D16" s="4">
+        <v>120.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="4">
         <v>74</v>
       </c>
-      <c r="B3">
+      <c r="B17" s="4">
         <v>2026</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>100.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>75</v>
-      </c>
-      <c r="B4">
+      <c r="C17" s="4">
+        <v>16</v>
+      </c>
+      <c r="D17" s="4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="4">
+        <v>88</v>
+      </c>
+      <c r="B18" s="4">
         <v>2026</v>
       </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>103.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>76</v>
-      </c>
-      <c r="B5">
-        <v>2026</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>104.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>77</v>
-      </c>
-      <c r="B6">
-        <v>2026</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>105.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>78</v>
-      </c>
-      <c r="B7">
-        <v>2026</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>105.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>79</v>
-      </c>
-      <c r="B8">
-        <v>2026</v>
-      </c>
-      <c r="C8">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>104.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>80</v>
-      </c>
-      <c r="B9">
-        <v>2026</v>
-      </c>
-      <c r="C9">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <v>106.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>81</v>
-      </c>
-      <c r="B10">
-        <v>2026</v>
-      </c>
-      <c r="C10">
-        <v>11</v>
-      </c>
-      <c r="D10">
-        <v>108.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>82</v>
-      </c>
-      <c r="B11">
-        <v>2026</v>
-      </c>
-      <c r="C11">
-        <v>12</v>
-      </c>
-      <c r="D11">
-        <v>110.8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>83</v>
-      </c>
-      <c r="B12">
-        <v>2026</v>
-      </c>
-      <c r="C12">
-        <v>13</v>
-      </c>
-      <c r="D12">
-        <v>113.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13">
-        <v>84</v>
-      </c>
-      <c r="B13">
-        <v>2026</v>
-      </c>
-      <c r="C13">
-        <v>14</v>
-      </c>
-      <c r="D13">
-        <v>115.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
-        <v>85</v>
-      </c>
-      <c r="B14">
-        <v>2026</v>
-      </c>
-      <c r="C14">
-        <v>15</v>
-      </c>
-      <c r="D14">
-        <v>116.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15">
-        <v>86</v>
-      </c>
-      <c r="B15">
-        <v>2026</v>
-      </c>
-      <c r="C15">
-        <v>16</v>
-      </c>
-      <c r="D15">
-        <v>118.6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16">
-        <v>87</v>
-      </c>
-      <c r="B16">
-        <v>2026</v>
-      </c>
-      <c r="C16">
+      <c r="C18" s="4">
         <v>17</v>
       </c>
-      <c r="D16">
-        <v>120.9</v>
+      <c r="D18" s="4">
+        <v>124.8</v>
       </c>
     </row>
   </sheetData>
@@ -10851,9 +11306,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -10930,7 +11385,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -11007,7 +11462,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -11084,7 +11539,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11161,7 +11616,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -11238,7 +11693,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -11315,7 +11770,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -11392,7 +11847,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -11469,7 +11924,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -11546,7 +12001,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -11623,7 +12078,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -11711,7 +12166,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -11787,7 +12242,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -11864,7 +12319,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -11941,7 +12396,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -12018,7 +12473,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -12095,7 +12550,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -12172,7 +12627,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -12249,7 +12704,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -12326,7 +12781,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -12403,7 +12858,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -12480,7 +12935,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -12568,7 +13023,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:23">
       <c r="B1">
@@ -12638,7 +13093,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -12709,7 +13164,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12780,7 +13235,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12851,7 +13306,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12922,7 +13377,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -12993,7 +13448,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -13064,7 +13519,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -13135,7 +13590,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -13206,7 +13661,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -13277,7 +13732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -13359,7 +13814,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -13435,7 +13890,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -13512,7 +13967,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -13589,7 +14044,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13666,7 +14121,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -13743,7 +14198,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -13820,7 +14275,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -13897,7 +14352,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -13974,7 +14429,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -14051,7 +14506,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -14128,7 +14583,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -14216,7 +14671,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -15073,9 +15528,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" customHeight="1">
@@ -15146,7 +15601,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -15217,7 +15672,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -15288,7 +15743,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -15359,7 +15814,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -15430,7 +15885,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -15501,7 +15956,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -15572,7 +16027,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -15643,7 +16098,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -15714,7 +16169,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -15785,7 +16240,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -15856,7 +16311,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.75">
+    <row r="12" spans="1:23" ht="15.4">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -15927,7 +16382,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.75">
+    <row r="13" spans="1:23" ht="15.4">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -15998,7 +16453,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.75">
+    <row r="14" spans="1:23" ht="15.4">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -16069,7 +16524,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.75">
+    <row r="15" spans="1:23" ht="15.4">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -16140,7 +16595,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.75">
+    <row r="16" spans="1:23" ht="15.4">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -16211,7 +16666,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.75">
+    <row r="17" spans="1:23" ht="15.4">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -16282,7 +16737,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.75">
+    <row r="18" spans="1:23" ht="15.4">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -16353,7 +16808,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="15.75">
+    <row r="19" spans="1:23" ht="15.4">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -16390,7 +16845,7 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="1:23" ht="15.75">
+    <row r="20" spans="1:23" ht="15.4">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -16431,7 +16886,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.75">
+    <row r="21" spans="1:23" ht="15.4">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -16478,7 +16933,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.75">
+    <row r="22" spans="1:23" ht="15.4">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -16549,7 +17004,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.75">
+    <row r="23" spans="1:23" ht="15.4">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -16631,9 +17086,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -16704,7 +17159,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -16775,7 +17230,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -16846,7 +17301,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -16917,7 +17372,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -16988,7 +17443,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -17059,7 +17514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -17130,7 +17585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -17201,7 +17656,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -17272,7 +17727,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -17343,7 +17798,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -17414,7 +17869,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.75">
+    <row r="12" spans="1:23" ht="15.4">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -17485,7 +17940,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.75">
+    <row r="13" spans="1:23" ht="15.4">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -17556,7 +18011,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.75">
+    <row r="14" spans="1:23" ht="15.4">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -17597,7 +18052,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.75">
+    <row r="15" spans="1:23" ht="15.4">
       <c r="A15" t="s">
         <v>79</v>
       </c>
@@ -17668,7 +18123,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.75">
+    <row r="16" spans="1:23" ht="15.4">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -17739,7 +18194,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.75">
+    <row r="17" spans="1:23" ht="15.4">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -17810,7 +18265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.75">
+    <row r="18" spans="1:23" ht="15.4">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -17847,7 +18302,7 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="1:23" ht="15.75">
+    <row r="19" spans="1:23" ht="15.4">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -17918,7 +18373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="15.75">
+    <row r="20" spans="1:23" ht="15.4">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -17989,7 +18444,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.75">
+    <row r="21" spans="1:23" ht="15.4">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -18036,7 +18491,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.75">
+    <row r="22" spans="1:23" ht="15.4">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -18107,7 +18562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.75">
+    <row r="23" spans="1:23" ht="15.4">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -18189,9 +18644,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -18268,7 +18723,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -18345,7 +18800,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -18422,7 +18877,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -18499,7 +18954,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -18576,7 +19031,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -18653,7 +19108,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -18730,7 +19185,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -18805,7 +19260,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -18882,7 +19337,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -18959,7 +19414,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -18992,7 +19447,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75">
+    <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -19023,7 +19478,7 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" spans="1:25" ht="15.75">
+    <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -19100,7 +19555,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.75">
+    <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -19131,7 +19586,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75">
+    <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -19172,7 +19627,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75">
+    <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -19247,7 +19702,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.75">
+    <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -19320,7 +19775,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.75">
+    <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -19385,7 +19840,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.75">
+    <row r="19" spans="1:25" ht="15.4">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -19462,7 +19917,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.75">
+    <row r="20" spans="1:25" ht="15.4">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -19539,7 +19994,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75">
+    <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -19616,7 +20071,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75">
+    <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -19693,7 +20148,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.75">
+    <row r="23" spans="1:25" ht="15.4">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -19770,7 +20225,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.75">
+    <row r="24" spans="1:25" ht="15.4">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -19847,7 +20302,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.75">
+    <row r="25" spans="1:25" ht="15.4">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -19894,7 +20349,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15.75">
+    <row r="26" spans="1:25" ht="15.4">
       <c r="A26" t="s">
         <v>41</v>
       </c>
